--- a/artfynd/A 39275-2022 artfynd.xlsx
+++ b/artfynd/A 39275-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1104,53 +1104,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103306902</v>
+        <v>135445924</v>
       </c>
       <c r="B6" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Estbergskojan, Storuman, Ly lm</t>
+          <t>Lankasjön öst, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616958</v>
+        <v>616980</v>
       </c>
       <c r="R6" t="n">
-        <v>7222150</v>
+        <v>7222181</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1174,12 +1169,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,22 +1199,762 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445924</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135445928</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lankasjön öst, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>617013</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7222213</v>
+      </c>
+      <c r="S7" t="n">
+        <v>18</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445928</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>103306902</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Estbergskojan, Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>616958</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7222150</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Carl Jansson</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Carl Jansson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/103306902</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135445921</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lankasjön öst, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>616988</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7222169</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Skalad stående död gran.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445921</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135445922</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lankasjön öst, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>616966</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7222146</v>
+      </c>
+      <c r="S10" t="n">
+        <v>27</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack + färsk skalad gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445922</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135445923</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lankasjön öst, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>616965</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7222155</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Skalad undervegetations gran. Mellanting färska/gamla spår</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445923</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135445929</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lankasjön öst, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>616956</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7222193</v>
+      </c>
+      <c r="S12" t="n">
+        <v>14</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Skalad stående död gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445929</t>
         </is>
       </c>
     </row>
@@ -1220,6 +1965,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39275-2022 artfynd.xlsx
+++ b/artfynd/A 39275-2022 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>135445924</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>135445928</v>
       </c>
       <c r="B7" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>135445921</v>
       </c>
       <c r="B9" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135445922</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>135445923</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>135445929</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
